--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -645,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N177"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -774,7 +773,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -840,7 +839,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -906,7 +905,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -972,7 +971,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1038,7 +1037,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1104,7 +1103,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1170,7 +1169,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1236,7 +1235,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1302,7 +1301,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1368,7 +1367,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1434,7 +1433,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1500,7 +1499,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1566,7 +1565,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1702,7 +1701,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1768,7 +1767,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1834,7 +1833,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1900,7 +1899,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1966,7 +1965,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2032,7 +2031,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2098,7 +2097,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2164,7 +2163,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2300,7 +2299,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2366,7 +2365,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2432,7 +2431,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2498,7 +2497,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2564,7 +2563,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2630,7 +2629,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2696,7 +2695,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2023-01-19</t>
+          <t>2023-01-20</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2762,7 +2761,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2023-01-19</t>
+          <t>2023-01-20</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2828,7 +2827,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2894,7 +2893,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2960,7 +2959,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-05-31</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3096,7 +3095,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3162,7 +3161,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3228,7 +3227,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3294,7 +3293,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3360,7 +3359,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3426,7 +3425,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3492,7 +3491,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3558,7 +3557,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3694,7 +3693,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3760,7 +3759,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3826,7 +3825,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3892,7 +3891,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3958,7 +3957,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4024,7 +4023,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4090,7 +4089,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4156,7 +4155,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4292,7 +4291,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4358,7 +4357,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4424,7 +4423,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4490,7 +4489,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4556,7 +4555,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4594,7 +4593,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4613,27 +4612,23 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>764</v>
+        <v>732</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>27020000</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>36913</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4642,12 +4637,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4657,14 +4652,14 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4683,7 +4678,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3695</v>
+        <v>3325</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4692,14 +4687,14 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>260000000</v>
+        <v>232800000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>70365</v>
+        <v>70015</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4730,7 +4725,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4749,27 +4744,23 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>764</v>
+        <v>732</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>26479600</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>36174</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4778,12 +4769,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4793,14 +4784,14 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4810,16 +4801,16 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1752</v>
+        <v>3325</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4828,14 +4819,14 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>90130000</v>
+        <v>218000000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>51444</v>
+        <v>65564</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4866,26 +4857,26 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1871</v>
+        <v>732</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4894,14 +4885,14 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>90130000</v>
+        <v>28540000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>48172</v>
+        <v>38989</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4932,7 +4923,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4942,36 +4933,32 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>764</v>
+        <v>1840</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>193000000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>104891</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4980,12 +4967,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -4995,14 +4982,14 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5012,16 +4999,16 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1752</v>
+        <v>2087</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5030,14 +5017,14 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>177650000</v>
+        <v>193000000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>101398</v>
+        <v>92477</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5068,26 +5055,26 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1755</v>
+        <v>732</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5096,14 +5083,14 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>177650000</v>
+        <v>25180000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>101225</v>
+        <v>34399</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5134,7 +5121,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5144,36 +5131,32 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>764</v>
+        <v>1840</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>83392000</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>45322</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5182,12 +5165,12 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -5197,14 +5180,14 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -5214,16 +5197,16 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1752</v>
+        <v>1973</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5232,14 +5215,14 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>86900000</v>
+        <v>113000000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>49600</v>
+        <v>57273</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5270,26 +5253,26 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1755</v>
+        <v>732</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5298,14 +5281,14 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>86900000</v>
+        <v>24747000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>49516</v>
+        <v>33807</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5336,7 +5319,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -5346,16 +5329,16 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>723</v>
+        <v>1722</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5364,14 +5347,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>24663000</v>
+        <v>81253000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>34112</v>
+        <v>47185</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5402,7 +5385,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5412,16 +5395,16 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1752</v>
+        <v>1972</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5430,14 +5413,14 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2023-02-15</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>93880000</v>
+        <v>98680000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>53584</v>
+        <v>50041</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5468,26 +5451,26 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1870</v>
+        <v>732</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5496,14 +5479,14 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>93280000</v>
+        <v>24310000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>49882</v>
+        <v>33210</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5534,7 +5517,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5544,16 +5527,16 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>723</v>
+        <v>1722</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5562,14 +5545,14 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>24174000</v>
+        <v>80000000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>33436</v>
+        <v>46458</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5600,7 +5583,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5610,16 +5593,16 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1752</v>
+        <v>1972</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5628,14 +5611,14 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>85500000</v>
+        <v>98000000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>48801</v>
+        <v>49696</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5666,26 +5649,26 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1755</v>
+        <v>732</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5694,14 +5677,14 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>84500000</v>
+        <v>23950000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>48148</v>
+        <v>32719</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5732,7 +5715,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5742,36 +5725,32 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>764</v>
+        <v>1722</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>78500000</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>45587</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5780,12 +5759,12 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -5795,14 +5774,14 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5812,16 +5791,16 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1752</v>
+        <v>1972</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5830,14 +5809,14 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>86750000</v>
+        <v>95687700</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>49515</v>
+        <v>48523</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5868,26 +5847,26 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>1755</v>
+        <v>732</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5896,14 +5875,14 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>85750000</v>
+        <v>23570000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>48860</v>
+        <v>32199</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5934,7 +5913,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5944,16 +5923,16 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>723</v>
+        <v>1722</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5962,14 +5941,14 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>23447160</v>
+        <v>76900000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>32430</v>
+        <v>44657</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6000,7 +5979,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -6010,16 +5989,16 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>1868</v>
+        <v>1972</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6028,14 +6007,14 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
-        <v>90600000</v>
+        <v>94800000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>48501</v>
+        <v>48073</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6066,26 +6045,26 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>1870</v>
+        <v>732</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6094,14 +6073,14 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>89600000</v>
+        <v>23500000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>47914</v>
+        <v>32104</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6132,7 +6111,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -6142,16 +6121,16 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>764</v>
+        <v>1722</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -6160,14 +6139,14 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>23813600</v>
+        <v>75800000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>31170</v>
+        <v>44019</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -6198,7 +6177,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -6208,16 +6187,16 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>1752</v>
+        <v>1972</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -6226,14 +6205,14 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
-        <v>82500000</v>
+        <v>91000000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>47089</v>
+        <v>46146</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6264,26 +6243,26 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>1755</v>
+        <v>732</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6292,14 +6271,14 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
-        <v>81490000</v>
+        <v>23150000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>46433</v>
+        <v>31626</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6330,7 +6309,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -6340,16 +6319,16 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>723</v>
+        <v>1722</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6358,14 +6337,14 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>22800000</v>
+        <v>74800000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>31535</v>
+        <v>43438</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6396,7 +6375,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -6406,16 +6385,16 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>1752</v>
+        <v>2088</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6424,14 +6403,14 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>95000000</v>
+        <v>89000000</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>54224</v>
+        <v>42625</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6462,26 +6441,26 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>1755</v>
+        <v>732</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6490,14 +6469,14 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>88000000</v>
+        <v>22800000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>50142</v>
+        <v>31148</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6528,7 +6507,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -6538,16 +6517,16 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>723</v>
+        <v>1722</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6556,14 +6535,14 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
-        <v>22580000</v>
+        <v>74000000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>31231</v>
+        <v>42973</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6594,7 +6573,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -6604,16 +6583,16 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>1752</v>
+        <v>1972</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -6622,14 +6601,14 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>87260000</v>
+        <v>88500000</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>49806</v>
+        <v>44878</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6660,26 +6639,26 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>1755</v>
+        <v>732</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6688,14 +6667,14 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>86350000</v>
+        <v>24250000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>49202</v>
+        <v>33128</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6726,7 +6705,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -6736,36 +6715,32 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>764</v>
+        <v>1722</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>73600000</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>42741</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6774,12 +6749,12 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
@@ -6789,14 +6764,14 @@
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -6806,16 +6781,16 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1752</v>
+        <v>1972</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6824,14 +6799,14 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2023-03-14</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>81400000</v>
+        <v>88000000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>46461</v>
+        <v>44625</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6862,26 +6837,26 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>1870</v>
+        <v>732</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -6890,14 +6865,14 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2023-03-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>80600000</v>
+        <v>27380000</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>43102</v>
+        <v>37404</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -6928,7 +6903,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -6938,16 +6913,16 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>723</v>
+        <v>1722</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -6956,14 +6931,14 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>22660000</v>
+        <v>72880000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>31342</v>
+        <v>42323</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -6994,7 +6969,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -7004,16 +6979,16 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>1868</v>
+        <v>1972</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -7022,14 +6997,14 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>86380000</v>
+        <v>87380000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>46242</v>
+        <v>44310</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7060,26 +7035,26 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1870</v>
+        <v>732</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7088,14 +7063,14 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>86000000</v>
+        <v>21750000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>45989</v>
+        <v>29713</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7126,7 +7101,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -7136,16 +7111,16 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>723</v>
+        <v>1722</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -7154,14 +7129,14 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>23520000</v>
+        <v>72000000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>32531</v>
+        <v>41812</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -7192,7 +7167,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -7202,16 +7177,16 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>1868</v>
+        <v>1972</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -7220,14 +7195,14 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
-        <v>81836250</v>
+        <v>86380000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>43810</v>
+        <v>43803</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -7258,26 +7233,26 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>1755</v>
+        <v>732</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -7286,14 +7261,14 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
-        <v>83000000</v>
+        <v>21400000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>47293</v>
+        <v>29235</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -7324,7 +7299,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -7334,16 +7309,16 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>723</v>
+        <v>1722</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -7352,14 +7327,14 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>23220000</v>
+        <v>70000000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>32116</v>
+        <v>40650</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7390,7 +7365,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -7400,16 +7375,16 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>1868</v>
+        <v>1972</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7418,14 +7393,14 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2023-03-27</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
-        <v>82000000</v>
+        <v>85480000</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>43897</v>
+        <v>43347</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7456,26 +7431,26 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>1870</v>
+        <v>772</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7484,14 +7459,14 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>80000000</v>
+        <v>26620000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>42781</v>
+        <v>34482</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7522,7 +7497,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -7532,36 +7507,32 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>764</v>
+        <v>1722</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>72450000</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>42073</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7570,12 +7541,12 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
@@ -7585,14 +7556,14 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -7602,16 +7573,16 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1752</v>
+        <v>1972</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7620,14 +7591,14 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
-        <v>81400000</v>
+        <v>83500000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>46461</v>
+        <v>42343</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7658,26 +7629,26 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>1755</v>
+        <v>732</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7686,14 +7657,14 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>88080000</v>
+        <v>22650000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>50188</v>
+        <v>30943</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7724,7 +7695,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -7734,16 +7705,16 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>723</v>
+        <v>1722</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7752,14 +7723,14 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>21850000</v>
+        <v>67500000</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>30221</v>
+        <v>39199</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7790,7 +7761,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7800,16 +7771,16 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>1752</v>
+        <v>1972</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -7818,14 +7789,14 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>75800000</v>
+        <v>80200000</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>43265</v>
+        <v>40669</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -7856,26 +7827,26 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>1870</v>
+        <v>732</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7884,14 +7855,14 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>81000000</v>
+        <v>20760000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>43316</v>
+        <v>28361</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7922,7 +7893,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -7932,36 +7903,32 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>764</v>
+        <v>1722</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>65200000</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>37863</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -7970,12 +7937,12 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
@@ -7985,14 +7952,14 @@
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -8002,16 +7969,16 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>1752</v>
+        <v>1972</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -8020,14 +7987,14 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>68000000</v>
+        <v>77800000</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>38813</v>
+        <v>39452</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -8058,26 +8025,26 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>1870</v>
+        <v>732</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -8086,14 +8053,14 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>68000000</v>
+        <v>20550000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>36364</v>
+        <v>28074</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -8124,7 +8091,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -8134,36 +8101,32 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>764</v>
+        <v>1723</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I114" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>63800000</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>37028</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -8172,12 +8135,12 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M114" s="3" t="inlineStr">
@@ -8187,14 +8150,14 @@
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -8204,16 +8167,16 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>1752</v>
+        <v>1973</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -8222,14 +8185,14 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>66600000</v>
+        <v>76280000</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>38014</v>
+        <v>38662</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -8260,26 +8223,26 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>1755</v>
+        <v>772</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -8288,14 +8251,14 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>65000000</v>
+        <v>22800000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>37037</v>
+        <v>29534</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8326,7 +8289,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -8336,16 +8299,16 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>723</v>
+        <v>1723</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8354,14 +8317,14 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>22470000</v>
+        <v>64500000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>31079</v>
+        <v>37435</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8392,7 +8355,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -8402,16 +8365,16 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>1752</v>
+        <v>1973</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -8420,14 +8383,14 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>68000000</v>
+        <v>78000000</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>38813</v>
+        <v>39534</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -8450,3904 +8413,6 @@
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>2座</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>1755</v>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="n">
-        <v>66000000</v>
-      </c>
-      <c r="I119" s="5" t="n">
-        <v>37607</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M119" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N119" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>27020000</v>
-      </c>
-      <c r="I120" s="5" t="n">
-        <v>36913</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M120" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N120" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="n">
-        <v>3325</v>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>2021-12-30</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="n">
-        <v>232800000</v>
-      </c>
-      <c r="I121" s="5" t="n">
-        <v>70015</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M121" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N121" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>26479600</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>36174</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M122" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N122" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="n">
-        <v>3325</v>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>2022-02-09</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>218000000</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>65564</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M123" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N123" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="n">
-        <v>28540000</v>
-      </c>
-      <c r="I124" s="5" t="n">
-        <v>38989</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M124" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N124" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="n">
-        <v>1840</v>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>193000000</v>
-      </c>
-      <c r="I125" s="5" t="n">
-        <v>104891</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L125" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M125" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N125" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="n">
-        <v>2087</v>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>193000000</v>
-      </c>
-      <c r="I126" s="5" t="n">
-        <v>92477</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M126" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N126" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>25180000</v>
-      </c>
-      <c r="I127" s="5" t="n">
-        <v>34399</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M127" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="n">
-        <v>1840</v>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="n">
-        <v>83392000</v>
-      </c>
-      <c r="I128" s="5" t="n">
-        <v>45322</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M128" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N128" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="n">
-        <v>1973</v>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="inlineStr">
-        <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="n">
-        <v>113000000</v>
-      </c>
-      <c r="I129" s="5" t="n">
-        <v>57273</v>
-      </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M129" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N129" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>24747000</v>
-      </c>
-      <c r="I130" s="5" t="n">
-        <v>33807</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M130" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N130" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>81253000</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>47185</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L131" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M131" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N131" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F132" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="H132" s="5" t="n">
-        <v>98680000</v>
-      </c>
-      <c r="I132" s="5" t="n">
-        <v>50041</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L132" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M132" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N132" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="n">
-        <v>24310000</v>
-      </c>
-      <c r="I133" s="5" t="n">
-        <v>33210</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M133" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N133" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>80000000</v>
-      </c>
-      <c r="I134" s="5" t="n">
-        <v>46458</v>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L134" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M134" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N134" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="n">
-        <v>98000000</v>
-      </c>
-      <c r="I135" s="5" t="n">
-        <v>49696</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M135" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N135" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="n">
-        <v>23950000</v>
-      </c>
-      <c r="I136" s="5" t="n">
-        <v>32719</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M136" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N136" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="n">
-        <v>78500000</v>
-      </c>
-      <c r="I137" s="5" t="n">
-        <v>45587</v>
-      </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M137" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N137" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="inlineStr">
-        <is>
-          <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="H138" s="5" t="n">
-        <v>95687700</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>48523</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M138" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N138" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="n">
-        <v>23570000</v>
-      </c>
-      <c r="I139" s="5" t="n">
-        <v>32199</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M139" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N139" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-19</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>76900000</v>
-      </c>
-      <c r="I140" s="5" t="n">
-        <v>44657</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M140" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N140" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="n">
-        <v>94800000</v>
-      </c>
-      <c r="I141" s="5" t="n">
-        <v>48073</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M141" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N141" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="n">
-        <v>23500000</v>
-      </c>
-      <c r="I142" s="5" t="n">
-        <v>32104</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M142" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N142" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="n">
-        <v>75800000</v>
-      </c>
-      <c r="I143" s="5" t="n">
-        <v>44019</v>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K143" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L143" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M143" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N143" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G144" s="3" t="inlineStr">
-        <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="n">
-        <v>91000000</v>
-      </c>
-      <c r="I144" s="5" t="n">
-        <v>46146</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M144" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N144" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="n">
-        <v>23150000</v>
-      </c>
-      <c r="I145" s="5" t="n">
-        <v>31626</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M145" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N145" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="n">
-        <v>74800000</v>
-      </c>
-      <c r="I146" s="5" t="n">
-        <v>43438</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M146" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N146" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="n">
-        <v>2088</v>
-      </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="n">
-        <v>89000000</v>
-      </c>
-      <c r="I147" s="5" t="n">
-        <v>42625</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M147" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N147" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="n">
-        <v>22800000</v>
-      </c>
-      <c r="I148" s="5" t="n">
-        <v>31148</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M148" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N148" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="n">
-        <v>74000000</v>
-      </c>
-      <c r="I149" s="5" t="n">
-        <v>42973</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M149" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N149" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G150" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="H150" s="5" t="n">
-        <v>88500000</v>
-      </c>
-      <c r="I150" s="5" t="n">
-        <v>44878</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M150" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N150" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="n">
-        <v>24250000</v>
-      </c>
-      <c r="I151" s="5" t="n">
-        <v>33128</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N151" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="H152" s="5" t="n">
-        <v>73600000</v>
-      </c>
-      <c r="I152" s="5" t="n">
-        <v>42741</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L152" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M152" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N152" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G153" s="3" t="inlineStr">
-        <is>
-          <t>2023-12-27</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="n">
-        <v>88000000</v>
-      </c>
-      <c r="I153" s="5" t="n">
-        <v>44625</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M153" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N153" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="H154" s="5" t="n">
-        <v>27380000</v>
-      </c>
-      <c r="I154" s="5" t="n">
-        <v>37404</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M154" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N154" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F155" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G155" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="H155" s="5" t="n">
-        <v>72880000</v>
-      </c>
-      <c r="I155" s="5" t="n">
-        <v>42323</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M155" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N155" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G156" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="H156" s="5" t="n">
-        <v>87380000</v>
-      </c>
-      <c r="I156" s="5" t="n">
-        <v>44310</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K156" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L156" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M156" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N156" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F157" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G157" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="n">
-        <v>21750000</v>
-      </c>
-      <c r="I157" s="5" t="n">
-        <v>29713</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M157" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N157" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F158" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G158" s="3" t="inlineStr">
-        <is>
-          <t>2024-03-11</t>
-        </is>
-      </c>
-      <c r="H158" s="5" t="n">
-        <v>72000000</v>
-      </c>
-      <c r="I158" s="5" t="n">
-        <v>41812</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K158" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L158" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M158" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N158" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E159" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F159" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G159" s="3" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="H159" s="5" t="n">
-        <v>86380000</v>
-      </c>
-      <c r="I159" s="5" t="n">
-        <v>43803</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M159" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N159" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F160" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G160" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="H160" s="5" t="n">
-        <v>21400000</v>
-      </c>
-      <c r="I160" s="5" t="n">
-        <v>29235</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M160" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N160" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F161" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G161" s="3" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="H161" s="5" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="I161" s="5" t="n">
-        <v>40650</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L161" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M161" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N161" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F162" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="inlineStr">
-        <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="H162" s="5" t="n">
-        <v>85480000</v>
-      </c>
-      <c r="I162" s="5" t="n">
-        <v>43347</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K162" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L162" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M162" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N162" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="n">
-        <v>772</v>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L163" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M163" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N163" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="H164" s="5" t="n">
-        <v>72450000</v>
-      </c>
-      <c r="I164" s="5" t="n">
-        <v>42073</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M164" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N164" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="H165" s="5" t="n">
-        <v>83500000</v>
-      </c>
-      <c r="I165" s="5" t="n">
-        <v>42343</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M165" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N165" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="H166" s="5" t="n">
-        <v>22650000</v>
-      </c>
-      <c r="I166" s="5" t="n">
-        <v>30943</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K166" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L166" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M166" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N166" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="n">
-        <v>67500000</v>
-      </c>
-      <c r="I167" s="5" t="n">
-        <v>39199</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M167" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N167" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G168" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="H168" s="5" t="n">
-        <v>80200000</v>
-      </c>
-      <c r="I168" s="5" t="n">
-        <v>40669</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M168" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N168" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F169" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G169" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="H169" s="5" t="n">
-        <v>20760000</v>
-      </c>
-      <c r="I169" s="5" t="n">
-        <v>28361</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M169" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="n">
-        <v>1722</v>
-      </c>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G170" s="3" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="H170" s="5" t="n">
-        <v>65200000</v>
-      </c>
-      <c r="I170" s="5" t="n">
-        <v>37863</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M170" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N170" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="n">
-        <v>1972</v>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="n">
-        <v>77800000</v>
-      </c>
-      <c r="I171" s="5" t="n">
-        <v>39452</v>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L171" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M171" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="n">
-        <v>732</v>
-      </c>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G172" s="3" t="inlineStr">
-        <is>
-          <t>2025-02-17</t>
-        </is>
-      </c>
-      <c r="H172" s="5" t="n">
-        <v>20550000</v>
-      </c>
-      <c r="I172" s="5" t="n">
-        <v>28074</v>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M172" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N172" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="H173" s="5" t="n">
-        <v>63800000</v>
-      </c>
-      <c r="I173" s="5" t="n">
-        <v>37028</v>
-      </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M173" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E174" s="4" t="n">
-        <v>1973</v>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="H174" s="5" t="n">
-        <v>76280000</v>
-      </c>
-      <c r="I174" s="5" t="n">
-        <v>38662</v>
-      </c>
-      <c r="J174" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M174" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N174" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>2房</t>
-        </is>
-      </c>
-      <c r="E175" s="4" t="n">
-        <v>772</v>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="H175" s="5" t="n">
-        <v>22800000</v>
-      </c>
-      <c r="I175" s="5" t="n">
-        <v>29534</v>
-      </c>
-      <c r="J175" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M175" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="H176" s="5" t="n">
-        <v>64500000</v>
-      </c>
-      <c r="I176" s="5" t="n">
-        <v>37435</v>
-      </c>
-      <c r="J176" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M176" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N176" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>3座</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E177" s="4" t="n">
-        <v>1973</v>
-      </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="H177" s="5" t="n">
-        <v>78000000</v>
-      </c>
-      <c r="I177" s="5" t="n">
-        <v>39534</v>
-      </c>
-      <c r="J177" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M177" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N177" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -12481,7 +8546,7 @@
           <t>A | 3330呎 (4+房)
 $23800万
 $71,471/呎
-(20年-11月-11日)</t>
+(20年-11月-12日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -12490,7 +8555,7 @@
           <t>C | 722呎 (2房)
 $2674万
 $37,036/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -12505,7 +8570,7 @@
           <t>A | 3330呎 (4+房)
 $21380万
 $64,204/呎
-(21年-04月-18日)</t>
+(21年-04月-19日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -12514,7 +8579,7 @@
           <t>C | 722呎 (2房)
 $2620万
 $36,288/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -12529,7 +8594,7 @@
           <t>A | 2141呎 (4+房)
 $12168万
 $56,833/呎
-(23年-05月-14日)</t>
+(23年-05月-15日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -12537,7 +8602,7 @@
           <t>B | 1842呎 (3房)
 $9512万
 $51,640/呎
-(23年-05月-14日)</t>
+(23年-05月-15日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -12545,7 +8610,7 @@
           <t>C | 764呎 (2房)
 $2544万
 $33,300/呎
-(24年-09月-02日)</t>
+(24年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -12560,7 +8625,7 @@
           <t>A | 2141呎 (4+房)
 $12018万
 $56,133/呎
-(23年-04月-16日)</t>
+(23年-04月-17日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -12568,7 +8633,7 @@
           <t>B | 1725呎 (3房)
 $9210万
 $53,391/呎
-(25年-08月-05日)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -12576,7 +8641,7 @@
           <t>C | 722呎 (2房)
 $2705万
 $37,465/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -12591,7 +8656,7 @@
           <t>A | 2024呎 (4+房)
 $11900万
 $58,794/呎
-(23年-03月-29日)</t>
+(23年-03月-30日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -12599,7 +8664,7 @@
           <t>B | 1724呎 (3房)
 $8800万
 $51,044/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -12607,7 +8672,7 @@
           <t>C | 722呎 (2房)
 $2466万
 $34,157/呎
-(24年-11月-13日)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -12622,7 +8687,7 @@
           <t>A | 2024呎 (4+房)
 $11800万
 $58,300/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -12630,7 +8695,7 @@
           <t>B | 1724呎 (3房)
 $8600万
 $49,884/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -12653,7 +8718,7 @@
           <t>A | 2140呎 (4+房)
 $11700万
 $54,673/呎
-(21年-10月-06日)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -12661,7 +8726,7 @@
           <t>B | 1724呎 (3房)
 $8500万
 $49,304/呎
-(25年-02月-12日)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -12669,7 +8734,7 @@
           <t>C | 722呎 (2房)
 $2382万
 $32,992/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -12684,7 +8749,7 @@
           <t>A | 2140呎 (4+房)
 $11500万
 $53,738/呎
-(20年-09月-09日)</t>
+(20年-09月-10日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -12692,7 +8757,7 @@
           <t>B | 1841呎 (3房)
 $9000万
 $48,886/呎
-(20年-12月-17日)</t>
+(20年-12月-18日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -12700,7 +8765,7 @@
           <t>C | 722呎 (2房)
 $2340万
 $32,410/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -12715,7 +8780,7 @@
           <t>A | 2140呎 (4+房)
 $11500万
 $53,738/呎
-(23年-01月-31日)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -12723,7 +8788,7 @@
           <t>B | 1724呎 (3房)
 $8380万
 $48,608/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -12746,7 +8811,7 @@
           <t>A | 2140呎 (4+房)
 $11300万
 $52,804/呎
-(22年-09月-25日)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -12754,7 +8819,7 @@
           <t>B | 1724呎 (3房)
 $8280万
 $48,028/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -12762,7 +8827,7 @@
           <t>C | 722呎 (2房)
 $2463万
 $34,111/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -12777,7 +8842,7 @@
           <t>A | 2140呎 (4+房)
 $11000万
 $51,402/呎
-(23年-01月-19日)</t>
+(23年-01月-20日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -12785,7 +8850,7 @@
           <t>B | 1841呎 (3房)
 $8900万
 $48,343/呎
-(23年-01月-19日)</t>
+(23年-01月-20日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -12793,7 +8858,7 @@
           <t>C | 722呎 (2房)
 $2510万
 $34,765/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -12808,7 +8873,7 @@
           <t>A | 2140呎 (4+房)
 $10500万
 $49,065/呎
-(22年-05月-30日)</t>
+(22年-05月-31日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -12816,7 +8881,7 @@
           <t>B | 1724呎 (3房)
 $8274万
 $47,993/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -12824,7 +8889,7 @@
           <t>C | 722呎 (2房)
 $2222万
 $30,776/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -12839,7 +8904,7 @@
           <t>A | 2140呎 (4+房)
 $10280万
 $48,037/呎
-(22年-05月-18日)</t>
+(22年-05月-19日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -12847,7 +8912,7 @@
           <t>B | 1724呎 (3房)
 $7950万
 $46,114/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -12870,7 +8935,7 @@
           <t>A | 2140呎 (4+房)
 $10270万
 $47,991/呎
-(23年-01月-26日)</t>
+(23年-01月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -12878,7 +8943,7 @@
           <t>B | 1724呎 (3房)
 $7838万
 $45,464/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -12886,7 +8951,7 @@
           <t>C | 722呎 (2房)
 $2178万
 $30,169/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -12901,7 +8966,7 @@
           <t>A | 2140呎 (4+房)
 $10450万
 $48,832/呎
-(23年-01月-30日)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -12909,7 +8974,7 @@
           <t>B | 1841呎 (3房)
 $8600万
 $46,714/呎
-(23年-01月-30日)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -12917,7 +8982,7 @@
           <t>C | 722呎 (2房)
 $2150万
 $29,778/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -12932,7 +8997,7 @@
           <t>A | 2140呎 (4+房)
 $9780万
 $45,701/呎
-(23年-02月-07日)</t>
+(23年-02月-08日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -12940,7 +9005,7 @@
           <t>B | 1841呎 (3房)
 $8020万
 $43,563/呎
-(23年-02月-07日)</t>
+(23年-02月-08日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -12963,7 +9028,7 @@
           <t>A | 2024呎 (4+房)
 $9680万
 $47,826/呎
-(23年-08月-28日)</t>
+(23年-08月-29日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -12971,7 +9036,7 @@
           <t>B | 1724呎 (3房)
 $8300万
 $48,144/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -12979,7 +9044,7 @@
           <t>C | 722呎 (2房)
 $2277万
 $31,537/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -12994,7 +9059,7 @@
           <t>A | 2024呎 (4+房)
 $8900万
 $43,972/呎
-(23年-12月-05日)</t>
+(23年-12月-06日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -13002,7 +9067,7 @@
           <t>B | 1724呎 (3房)
 $6900万
 $40,023/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -13010,7 +9075,7 @@
           <t>C | 722呎 (2房)
 $2254万
 $31,219/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -13025,7 +9090,7 @@
           <t>A | 2141呎 (4+房)
 $9300万
 $43,438/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -13033,7 +9098,7 @@
           <t>B | 1725呎 (3房)
 $7030万
 $40,754/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -13056,7 +9121,7 @@
           <t>A | 2141呎 (4+房)
 $8600万
 $40,168/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -13064,7 +9129,7 @@
           <t>B | 1725呎 (3房)
 $6808万
 $39,467/呎
-(25年-02月-17日)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -13072,7 +9137,7 @@
           <t>C | 722呎 (2房)
 $2247万
 $31,122/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -13103,7 +9168,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>2座 销控网格图</t>
+          <t>3座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -13142,12 +9207,12 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -13157,737 +9222,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 3695呎 (4+房)
-$26000万
-$70,365/呎
-(21年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1871呎 (3房)
-$9013万
-$48,172/呎
-(24年-11月-27日)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$9013万
-$51,444/呎
-(24年-11月-27日)</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$17765万
-$101,225/呎
-(24年-11月-03日)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$17765万
-$101,398/呎
-(24年-11月-03日)</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8690万
-$49,516/呎
-(24年-11月-28日)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8690万
-$49,600/呎
-(24年-11月-28日)</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$9328万
-$49,882/呎
-(21年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$9388万
-$53,584/呎
-(23年-02月-15日)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2466万
-$34,112/呎
-(25年-05月-27日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8450万
-$48,148/呎
-(25年-02月-20日)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8550万
-$48,801/呎
-(25年-02月-20日)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2417万
-$33,436/呎
-(25年-02月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8575万
-$48,860/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8675万
-$49,515/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8960万
-$47,914/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 1868呎 (3房)
-$9060万
-$48,501/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2345万
-$32,430/呎
-(24年-10月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8149万
-$46,433/呎
-(25年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8250万
-$47,089/呎
-(25年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-$2381万
-$31,170/呎
-(25年-11月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8800万
-$50,142/呎
-(25年-09月-22日)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$9500万
-$54,224/呎
-(24年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2280万
-$31,535/呎
-(24年-11月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8635万
-$49,202/呎
-(23年-02月-02日)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8726万
-$49,806/呎
-(23年-02月-02日)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2258万
-$31,231/呎
-(25年-02月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8060万
-$43,102/呎
-(23年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8140万
-$46,461/呎
-(23年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8600万
-$45,989/呎
-(20年-08月-27日)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 1868呎 (3房)
-$8638万
-$46,242/呎
-(23年-03月-26日)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2266万
-$31,342/呎
-(25年-12月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8300万
-$47,293/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 1868呎 (3房)
-$8184万
-$43,810/呎
-(23年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2352万
-$32,531/呎
-(26年-06月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8000万
-$42,781/呎
-(22年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 1868呎 (3房)
-$8200万
-$43,897/呎
-(23年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2322万
-$32,116/呎
-(26年-06月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8808万
-$50,188/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8140万
-$46,461/呎
-(24年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8100万
-$43,316/呎
-(23年-03月-07日)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$7580万
-$43,265/呎
-(25年-11月-11日)</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2185万
-$30,221/呎
-(26年-02月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$6800万
-$36,364/呎
-(25年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$6800万
-$38,813/呎
-(25年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$6500万
-$37,037/呎
-(25年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$6660万
-$38,014/呎
-(25年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$6600万
-$37,607/呎
-(25年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$6800万
-$38,813/呎
-(24年-11月-17日)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2247万
-$31,079/呎
-(26年-02月-22日)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -13934,7 +9269,7 @@
           <t>A | 3325呎 (4+房)
 $23280万
 $70,015/呎
-(21年-12月-30日)</t>
+(21年-12月-31日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -13943,7 +9278,7 @@
           <t>C | 732呎 (2房)
 $2702万
 $36,913/呎
-(24年-09月-11日)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -13958,7 +9293,7 @@
           <t>A | 3325呎 (4+房)
 $21800万
 $65,564/呎
-(22年-02月-09日)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -13967,7 +9302,7 @@
           <t>C | 732呎 (2房)
 $2648万
 $36,174/呎
-(24年-09月-11日)</t>
+(24年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -13982,7 +9317,7 @@
           <t>A | 2087呎 (4+房)
 $19300万
 $92,477/呎
-(24年-09月-19日)</t>
+(24年-09月-20日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -13990,7 +9325,7 @@
           <t>B | 1840呎 (3房)
 $19300万
 $104,891/呎
-(24年-09月-19日)</t>
+(24年-09月-20日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -13998,7 +9333,7 @@
           <t>C | 732呎 (2房)
 $2854万
 $38,989/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -14013,7 +9348,7 @@
           <t>A | 1973呎 (4+房)
 $11300万
 $57,273/呎
-(23年-05月-09日)</t>
+(23年-05月-10日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -14021,7 +9356,7 @@
           <t>B | 1840呎 (3房)
 $8339万
 $45,322/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -14029,7 +9364,7 @@
           <t>C | 732呎 (2房)
 $2518万
 $34,399/呎
-(24年-11月-19日)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -14044,7 +9379,7 @@
           <t>A | 1972呎 (4+房)
 $9868万
 $50,041/呎
-(24年-10月-07日)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -14052,7 +9387,7 @@
           <t>B | 1722呎 (3房)
 $8125万
 $47,185/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -14060,7 +9395,7 @@
           <t>C | 732呎 (2房)
 $2475万
 $33,807/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -14075,7 +9410,7 @@
           <t>A | 1972呎 (4+房)
 $9800万
 $49,696/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -14083,7 +9418,7 @@
           <t>B | 1722呎 (3房)
 $8000万
 $46,458/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -14091,7 +9426,7 @@
           <t>C | 732呎 (2房)
 $2431万
 $33,210/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -14106,7 +9441,7 @@
           <t>A | 1972呎 (4+房)
 $9569万
 $48,523/呎
-(24年-06月-05日)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -14114,7 +9449,7 @@
           <t>B | 1722呎 (3房)
 $7850万
 $45,587/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -14122,7 +9457,7 @@
           <t>C | 732呎 (2房)
 $2395万
 $32,719/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -14137,7 +9472,7 @@
           <t>A | 1972呎 (4+房)
 $9480万
 $48,073/呎
-(24年-07月-25日)</t>
+(24年-07月-26日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -14145,7 +9480,7 @@
           <t>B | 1722呎 (3房)
 $7690万
 $44,657/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -14153,7 +9488,7 @@
           <t>C | 732呎 (2房)
 $2357万
 $32,199/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -14168,7 +9503,7 @@
           <t>A | 1972呎 (4+房)
 $9100万
 $46,146/呎
-(24年-08月-26日)</t>
+(24年-08月-27日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -14176,7 +9511,7 @@
           <t>B | 1722呎 (3房)
 $7580万
 $44,019/呎
-(24年-08月-26日)</t>
+(24年-08月-27日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -14184,7 +9519,7 @@
           <t>C | 732呎 (2房)
 $2350万
 $32,104/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -14199,7 +9534,7 @@
           <t>A | 2088呎 (4+房)
 $8900万
 $42,625/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -14207,7 +9542,7 @@
           <t>B | 1722呎 (3房)
 $7480万
 $43,438/呎
-(24年-07月-30日)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -14215,7 +9550,7 @@
           <t>C | 732呎 (2房)
 $2315万
 $31,626/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -14230,7 +9565,7 @@
           <t>A | 1972呎 (4+房)
 $8850万
 $44,878/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -14238,7 +9573,7 @@
           <t>B | 1722呎 (3房)
 $7400万
 $42,973/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -14246,7 +9581,7 @@
           <t>C | 732呎 (2房)
 $2280万
 $31,148/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -14261,7 +9596,7 @@
           <t>A | 1972呎 (4+房)
 $8800万
 $44,625/呎
-(23年-12月-27日)</t>
+(23年-12月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -14269,7 +9604,7 @@
           <t>B | 1722呎 (3房)
 $7360万
 $42,741/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -14277,7 +9612,7 @@
           <t>C | 732呎 (2房)
 $2425万
 $33,128/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -14292,7 +9627,7 @@
           <t>A | 1972呎 (4+房)
 $8738万
 $44,310/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -14300,7 +9635,7 @@
           <t>B | 1722呎 (3房)
 $7288万
 $42,323/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -14308,7 +9643,7 @@
           <t>C | 732呎 (2房)
 $2738万
 $37,404/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -14323,7 +9658,7 @@
           <t>A | 1972呎 (4+房)
 $8638万
 $43,803/呎
-(24年-08月-27日)</t>
+(24年-08月-28日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -14331,7 +9666,7 @@
           <t>B | 1722呎 (3房)
 $7200万
 $41,812/呎
-(24年-03月-11日)</t>
+(24年-03月-12日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -14339,7 +9674,7 @@
           <t>C | 732呎 (2房)
 $2175万
 $29,713/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -14354,7 +9689,7 @@
           <t>A | 1972呎 (4+房)
 $8548万
 $43,347/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -14362,7 +9697,7 @@
           <t>B | 1722呎 (3房)
 $7000万
 $40,650/呎
-(24年-07月-16日)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -14370,7 +9705,7 @@
           <t>C | 732呎 (2房)
 $2140万
 $29,235/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
     </row>
@@ -14385,7 +9720,7 @@
           <t>A | 1972呎 (4+房)
 $8350万
 $42,343/呎
-(24年-08月-26日)</t>
+(24年-08月-27日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -14393,15 +9728,15 @@
           <t>B | 1722呎 (3房)
 $7245万
 $42,073/呎
-(24年-04月-11日)</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
+(24年-04月-12日)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 772呎 (2房)
-招标单位
--
-(在售)</t>
+$2662万
+$34,482/呎
+(26年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -14416,7 +9751,7 @@
           <t>A | 1972呎 (4+房)
 $8020万
 $40,669/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -14424,7 +9759,7 @@
           <t>B | 1722呎 (3房)
 $6750万
 $39,199/呎
-(24年-06月-17日)</t>
+(24年-06月-18日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -14432,7 +9767,7 @@
           <t>C | 732呎 (2房)
 $2265万
 $30,943/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -14447,7 +9782,7 @@
           <t>A | 1972呎 (4+房)
 $7780万
 $39,452/呎
-(24年-07月-07日)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -14455,7 +9790,7 @@
           <t>B | 1722呎 (3房)
 $6520万
 $37,863/呎
-(24年-07月-17日)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -14463,7 +9798,7 @@
           <t>C | 732呎 (2房)
 $2076万
 $28,361/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -14478,7 +9813,7 @@
           <t>A | 1973呎 (4+房)
 $7628万
 $38,662/呎
-(24年-09月-04日)</t>
+(24年-09月-05日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -14486,7 +9821,7 @@
           <t>B | 1723呎 (3房)
 $6380万
 $37,028/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -14494,7 +9829,7 @@
           <t>C | 732呎 (2房)
 $2055万
 $28,074/呎
-(25年-02月-17日)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -14509,7 +9844,7 @@
           <t>A | 1973呎 (4+房)
 $7800万
 $39,534/呎
-(24年-11月-13日)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -14517,7 +9852,7 @@
           <t>B | 1723呎 (3房)
 $6450万
 $37,435/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -14525,7 +9860,7 @@
           <t>C | 772呎 (2房)
 $2280万
 $29,534/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -644,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4593,7 +4594,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4612,23 +4613,27 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>27020000</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>36913</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4637,12 +4642,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4652,14 +4657,14 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4678,7 +4683,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3325</v>
+        <v>3695</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4687,14 +4692,14 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>232800000</v>
+        <v>260000000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>70015</v>
+        <v>70365</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4725,7 +4730,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4744,23 +4749,27 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>26479600</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>36174</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4769,12 +4778,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4784,14 +4793,14 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4801,16 +4810,16 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>3325</v>
+        <v>1752</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4819,14 +4828,14 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>218000000</v>
+        <v>90130000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>65564</v>
+        <v>51444</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4857,26 +4866,26 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>732</v>
+        <v>1871</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4885,14 +4894,14 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>28540000</v>
+        <v>90130000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>38989</v>
+        <v>48172</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4923,7 +4932,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4933,32 +4942,36 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1840</v>
+        <v>764</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>193000000</v>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>104891</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4967,12 +4980,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -4982,14 +4995,14 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4999,16 +5012,16 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2087</v>
+        <v>1752</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5017,14 +5030,14 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>193000000</v>
+        <v>177650000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>92477</v>
+        <v>101398</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5055,26 +5068,26 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>732</v>
+        <v>1755</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5083,14 +5096,14 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>25180000</v>
+        <v>177650000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>34399</v>
+        <v>101225</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5121,7 +5134,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5131,32 +5144,36 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1840</v>
+        <v>764</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>83392000</v>
-      </c>
-      <c r="I69" s="5" t="n">
-        <v>45322</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5165,12 +5182,12 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -5180,14 +5197,14 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -5197,16 +5214,16 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1973</v>
+        <v>1752</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5215,14 +5232,14 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>113000000</v>
+        <v>86900000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>57273</v>
+        <v>49600</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5253,26 +5270,26 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>732</v>
+        <v>1755</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5281,14 +5298,14 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>24747000</v>
+        <v>86900000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>33807</v>
+        <v>49516</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5319,7 +5336,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -5329,16 +5346,16 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1722</v>
+        <v>723</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5347,14 +5364,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>81253000</v>
+        <v>24663000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>47185</v>
+        <v>34112</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5385,7 +5402,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5395,16 +5412,16 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1972</v>
+        <v>1752</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5413,14 +5430,14 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2023-02-16</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>98680000</v>
+        <v>93880000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>50041</v>
+        <v>53584</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5451,26 +5468,26 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>732</v>
+        <v>1870</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5479,14 +5496,14 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>24310000</v>
+        <v>93280000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>33210</v>
+        <v>49882</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5517,7 +5534,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5527,16 +5544,16 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1722</v>
+        <v>723</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5545,14 +5562,14 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>80000000</v>
+        <v>24174000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>46458</v>
+        <v>33436</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5583,7 +5600,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5593,16 +5610,16 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1972</v>
+        <v>1752</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5611,14 +5628,14 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>98000000</v>
+        <v>85500000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>49696</v>
+        <v>48801</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5649,26 +5666,26 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>732</v>
+        <v>1755</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5677,14 +5694,14 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>23950000</v>
+        <v>84500000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>32719</v>
+        <v>48148</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5715,7 +5732,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5725,32 +5742,36 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1722</v>
+        <v>764</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>78500000</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>45587</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5759,12 +5780,12 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -5774,14 +5795,14 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5791,16 +5812,16 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1972</v>
+        <v>1752</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5809,14 +5830,14 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>95687700</v>
+        <v>86750000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>48523</v>
+        <v>49515</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5847,26 +5868,26 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>732</v>
+        <v>1755</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5875,14 +5896,14 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>23570000</v>
+        <v>85750000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>32199</v>
+        <v>48860</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5913,7 +5934,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5923,16 +5944,16 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>1722</v>
+        <v>723</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5941,14 +5962,14 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>76900000</v>
+        <v>23447160</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>44657</v>
+        <v>32430</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5979,7 +6000,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -5989,16 +6010,16 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>1972</v>
+        <v>1868</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6007,14 +6028,14 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
-        <v>94800000</v>
+        <v>90600000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>48073</v>
+        <v>48501</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6045,26 +6066,26 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>732</v>
+        <v>1870</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6073,14 +6094,14 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>23500000</v>
+        <v>89600000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>32104</v>
+        <v>47914</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6111,7 +6132,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -6121,16 +6142,16 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>1722</v>
+        <v>764</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -6139,14 +6160,14 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>75800000</v>
+        <v>23813600</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>44019</v>
+        <v>31170</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -6177,7 +6198,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -6187,16 +6208,16 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>1972</v>
+        <v>1752</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -6205,14 +6226,14 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
-        <v>91000000</v>
+        <v>82500000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>46146</v>
+        <v>47089</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6243,26 +6264,26 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>732</v>
+        <v>1755</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6271,14 +6292,14 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
-        <v>23150000</v>
+        <v>81490000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>31626</v>
+        <v>46433</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6309,7 +6330,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -6319,16 +6340,16 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>1722</v>
+        <v>723</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6337,14 +6358,14 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>74800000</v>
+        <v>22800000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>43438</v>
+        <v>31535</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6375,7 +6396,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -6385,16 +6406,16 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>2088</v>
+        <v>1752</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6403,14 +6424,14 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>89000000</v>
+        <v>95000000</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>42625</v>
+        <v>54224</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6441,26 +6462,26 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>732</v>
+        <v>1755</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6469,14 +6490,14 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>22800000</v>
+        <v>88000000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>31148</v>
+        <v>50142</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6507,7 +6528,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -6517,16 +6538,16 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>1722</v>
+        <v>723</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6535,14 +6556,14 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
-        <v>74000000</v>
+        <v>22580000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>42973</v>
+        <v>31231</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6573,7 +6594,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -6583,16 +6604,16 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>1972</v>
+        <v>1752</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -6601,14 +6622,14 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>88500000</v>
+        <v>87260000</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>44878</v>
+        <v>49806</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6639,26 +6660,26 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>732</v>
+        <v>1755</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6667,14 +6688,14 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>24250000</v>
+        <v>86350000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>33128</v>
+        <v>49202</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6705,7 +6726,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -6715,32 +6736,36 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>1722</v>
+        <v>764</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>73600000</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>42741</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6749,12 +6774,12 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
@@ -6764,14 +6789,14 @@
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -6781,16 +6806,16 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1972</v>
+        <v>1752</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6799,14 +6824,14 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>88000000</v>
+        <v>81400000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>44625</v>
+        <v>46461</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6837,26 +6862,26 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>732</v>
+        <v>1870</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -6865,14 +6890,14 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>27380000</v>
+        <v>80600000</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>37404</v>
+        <v>43102</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -6903,7 +6928,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -6913,16 +6938,16 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>1722</v>
+        <v>723</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -6931,14 +6956,14 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>72880000</v>
+        <v>22660000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>42323</v>
+        <v>31342</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -6969,7 +6994,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -6979,16 +7004,16 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>1972</v>
+        <v>1868</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -6997,14 +7022,14 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2023-03-27</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>87380000</v>
+        <v>86380000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>44310</v>
+        <v>46242</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7035,26 +7060,26 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>732</v>
+        <v>1870</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7063,14 +7088,14 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>21750000</v>
+        <v>86000000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>29713</v>
+        <v>45989</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7101,7 +7126,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -7111,16 +7136,16 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>1722</v>
+        <v>723</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -7129,14 +7154,14 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>72000000</v>
+        <v>23520000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>41812</v>
+        <v>32531</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -7167,7 +7192,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -7177,16 +7202,16 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>1972</v>
+        <v>1868</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -7195,14 +7220,14 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
-        <v>86380000</v>
+        <v>81836250</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>43803</v>
+        <v>43810</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -7233,26 +7258,26 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>732</v>
+        <v>1755</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -7261,14 +7286,14 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
-        <v>21400000</v>
+        <v>83000000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>29235</v>
+        <v>47293</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -7299,7 +7324,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -7309,16 +7334,16 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1722</v>
+        <v>723</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -7327,14 +7352,14 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>70000000</v>
+        <v>23220000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>40650</v>
+        <v>32116</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7365,7 +7390,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -7375,16 +7400,16 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>1972</v>
+        <v>1868</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7393,14 +7418,14 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
-        <v>85480000</v>
+        <v>82000000</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>43347</v>
+        <v>43897</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7431,26 +7456,26 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>772</v>
+        <v>1870</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7459,14 +7484,14 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>26620000</v>
+        <v>80000000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>34482</v>
+        <v>42781</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7497,7 +7522,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -7507,32 +7532,36 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>1722</v>
+        <v>764</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>72450000</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>42073</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7541,12 +7570,12 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
@@ -7556,14 +7585,14 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -7573,16 +7602,16 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1972</v>
+        <v>1752</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7591,14 +7620,14 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
-        <v>83500000</v>
+        <v>81400000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>42343</v>
+        <v>46461</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7629,26 +7658,26 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>732</v>
+        <v>1755</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7657,14 +7686,14 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>22650000</v>
+        <v>88080000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>30943</v>
+        <v>50188</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7695,7 +7724,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -7705,16 +7734,16 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>1722</v>
+        <v>723</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7723,14 +7752,14 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>67500000</v>
+        <v>21850000</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>39199</v>
+        <v>30221</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7761,7 +7790,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7771,16 +7800,16 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>1972</v>
+        <v>1752</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -7789,14 +7818,14 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>80200000</v>
+        <v>75800000</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>40669</v>
+        <v>43265</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -7827,26 +7856,26 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>732</v>
+        <v>1870</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7855,14 +7884,14 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>20760000</v>
+        <v>81000000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>28361</v>
+        <v>43316</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7893,7 +7922,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -7903,32 +7932,36 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>1722</v>
+        <v>764</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>65200000</v>
-      </c>
-      <c r="I111" s="5" t="n">
-        <v>37863</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -7937,12 +7970,12 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
@@ -7952,14 +7985,14 @@
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -7969,16 +8002,16 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>1972</v>
+        <v>1752</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -7987,14 +8020,14 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>77800000</v>
+        <v>68000000</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>39452</v>
+        <v>38813</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -8025,26 +8058,26 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>732</v>
+        <v>1870</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -8053,14 +8086,14 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>20550000</v>
+        <v>68000000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>28074</v>
+        <v>36364</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -8091,7 +8124,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -8101,16 +8134,16 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>1723</v>
+        <v>764</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -8119,14 +8152,14 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>63800000</v>
+        <v>26210000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>37028</v>
+        <v>34306</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -8157,7 +8190,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -8167,16 +8200,16 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>1973</v>
+        <v>1752</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -8185,14 +8218,14 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>76280000</v>
+        <v>66600000</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>38662</v>
+        <v>38014</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -8223,26 +8256,26 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>772</v>
+        <v>1755</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -8251,14 +8284,14 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>22800000</v>
+        <v>65000000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>29534</v>
+        <v>37037</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8289,7 +8322,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -8299,16 +8332,16 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>1723</v>
+        <v>723</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8317,14 +8350,14 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>64500000</v>
+        <v>22470000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>37435</v>
+        <v>31079</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8355,64 +8388,3958 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
+          <t>2座</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>1752</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>38813</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>2座</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>1755</v>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>37607</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
           <t>3座</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>27020000</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>36913</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>3325</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>232800000</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>70015</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>26479600</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>36174</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>3325</v>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>65564</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>28540000</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>38989</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>1840</v>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>193000000</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>104891</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>2087</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>193000000</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>92477</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>25180000</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>34399</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>1840</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>83392000</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>45322</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>57273</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>24747000</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>33807</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>81253000</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>47185</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>98680000</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>50041</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>24310000</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>33210</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>46458</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>98000000</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>49696</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>23950000</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>32719</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>78500000</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>45587</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>95687700</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>48523</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>23570000</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>32199</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>76900000</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>44657</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>94800000</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>48073</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>23500000</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>32104</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>75800000</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>44019</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>46146</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>23150000</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>31626</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>74800000</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>43438</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="n">
+        <v>2088</v>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>42625</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>22800000</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>31148</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>42973</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>88500000</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>44878</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>24250000</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>33128</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>73600000</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>42741</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>88000000</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>44625</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>27380000</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>37404</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>72880000</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>42323</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>87380000</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>44310</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>21750000</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>29713</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>72000000</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>41812</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>86380000</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>43803</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>21400000</v>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>29235</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="I161" s="5" t="n">
+        <v>40650</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>85480000</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>43347</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>772</v>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>26620000</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>34482</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>72450000</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>42073</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="n">
+        <v>83500000</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>42343</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>22650000</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>30943</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>67500000</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>39199</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>80200000</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>40669</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>20760000</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>28361</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>65200000</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>37863</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>77800000</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>39452</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>20550000</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>28074</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>63800000</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>37028</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>76280000</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>38662</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>2房</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="n">
+        <v>772</v>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="n">
+        <v>22800000</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>29534</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>64500000</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>37435</v>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>3座</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E118" s="4" t="n">
+      <c r="E177" s="4" t="n">
         <v>1973</v>
       </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H118" s="5" t="n">
+      <c r="H177" s="5" t="n">
         <v>78000000</v>
       </c>
-      <c r="I118" s="5" t="n">
+      <c r="I177" s="5" t="n">
         <v>39534</v>
       </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M118" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N118" s="3" t="inlineStr">
+      <c r="J177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -9168,6 +13095,736 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3695呎 (4+房)
+$26000万
+$70,365/呎
+(21年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1871呎 (3房)
+$9013万
+$48,172/呎
+(24年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$9013万
+$51,444/呎
+(24年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$17765万
+$101,225/呎
+(24年-11月-04日)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$17765万
+$101,398/呎
+(24年-11月-04日)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8690万
+$49,516/呎
+(24年-11月-29日)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8690万
+$49,600/呎
+(24年-11月-29日)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$9328万
+$49,882/呎
+(21年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$9388万
+$53,584/呎
+(23年-02月-16日)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2466万
+$34,112/呎
+(25年-05月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8450万
+$48,148/呎
+(25年-02月-21日)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8550万
+$48,801/呎
+(25年-02月-21日)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2417万
+$33,436/呎
+(25年-02月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8575万
+$48,860/呎
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8675万
+$49,515/呎
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8960万
+$47,914/呎
+(21年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1868呎 (3房)
+$9060万
+$48,501/呎
+(21年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2345万
+$32,430/呎
+(24年-10月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8149万
+$46,433/呎
+(25年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8250万
+$47,089/呎
+(25年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+$2381万
+$31,170/呎
+(25年-11月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8800万
+$50,142/呎
+(25年-09月-23日)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$9500万
+$54,224/呎
+(24年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2280万
+$31,535/呎
+(24年-11月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8635万
+$49,202/呎
+(23年-02月-03日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8726万
+$49,806/呎
+(23年-02月-03日)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2258万
+$31,231/呎
+(25年-02月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8060万
+$43,102/呎
+(23年-03月-15日)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8140万
+$46,461/呎
+(23年-03月-15日)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8600万
+$45,989/呎
+(20年-08月-28日)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1868呎 (3房)
+$8638万
+$46,242/呎
+(23年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2266万
+$31,342/呎
+(25年-12月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8300万
+$47,293/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1868呎 (3房)
+$8184万
+$43,810/呎
+(23年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2352万
+$32,531/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8000万
+$42,781/呎
+(22年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1868呎 (3房)
+$8200万
+$43,897/呎
+(23年-03月-28日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2322万
+$32,116/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8808万
+$50,188/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8140万
+$46,461/呎
+(24年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8100万
+$43,316/呎
+(23年-03月-08日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$7580万
+$43,265/呎
+(25年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2185万
+$30,221/呎
+(26年-02月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$6800万
+$36,364/呎
+(25年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$6800万
+$38,813/呎
+(25年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$6500万
+$37,037/呎
+(25年-05月-30日)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$6660万
+$38,014/呎
+(25年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+$2621万
+$34,306/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$6600万
+$37,607/呎
+(25年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$6800万
+$38,813/呎
+(24年-11月-18日)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2247万
+$31,079/呎
+(26年-02月-23日)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
           <t>3座 销控网格图</t>
         </is>
       </c>

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2141</v>
+        <v>2024</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4358,14 +4358,14 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
         <v>93000000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>43438</v>
+        <v>45949</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -13014,10 +13014,10 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 2141呎 (4+房)
+          <t>A | 2024呎 (4+房)
 $9300万
-$43,438/呎
-(26年-07月-15日)</t>
+$45,949/呎
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>772</v>
+        <v>732</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -11386,14 +11386,14 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
         <v>26620000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>34482</v>
+        <v>36366</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -14390,10 +14390,10 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 772呎 (2房)
+          <t>C | 732呎 (2房)
 $2662万
-$34,482/呎
-(26年-07月-27日)</t>
+$36,366/呎
+(26年-08月-17日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>764</v>
+        <v>723</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -8152,14 +8152,14 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
         <v>26210000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>34306</v>
+        <v>36252</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -13760,10 +13760,10 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>C | 764呎 (2房)
+          <t>C | 723呎 (2房)
 $2621万
-$34,306/呎
-(26年-07月-28日)</t>
+$36,252/呎
+(26年-08月-20日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3695</v>
+        <v>3559</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>260000000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>70365</v>
+        <v>73054</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -13193,9 +13193,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 3695呎 (4+房)
+          <t>A | 3559呎 (4+房)
 $26000万
-$70,365/呎
+$73,054/呎
 (21年-06月-30日)</t>
         </is>
       </c>

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -4753,23 +4753,19 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>29680000</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>38848</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4778,12 +4774,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4793,7 +4789,7 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13135,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -13149,7 +13145,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -13231,12 +13227,12 @@
 (24年-11月-28日)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
+$2968万
+$38,848/呎
+(26年-09月-01日)</t>
         </is>
       </c>
     </row>
